--- a/datos/convenios_semaforo_agosto2026_verificado.xlsx
+++ b/datos/convenios_semaforo_agosto2026_verificado.xlsx
@@ -1,42 +1,42 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roberto\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9037DF3F-B3D2-44A5-A773-F0A687DBD7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="t3txaPesER2/VrXFsBDSBf36+OGeMkuYrWi2cz87c7Q="/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Hojas de cálculo</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>2</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="2" baseType="lpstr">
+      <vt:lpstr>Hoja1</vt:lpstr>
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>ROBERTO ANTONIO ROJAS ARCA - CS</dc:creator>
+  <cp:lastModifiedBy>Roberto</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-04-06T21:13:55Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-04T19:56:57Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="464">
   <si>
     <t>BANCO PRODUCTOR</t>
@@ -1438,7 +1438,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
@@ -2050,7 +2050,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
@@ -2246,7 +2246,44 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roberto\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9037DF3F-B3D2-44A5-A773-F0A687DBD7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="t3txaPesER2/VrXFsBDSBf36+OGeMkuYrWi2cz87c7Q="/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
@@ -7724,32 +7761,6 @@
       <c r="H238" s="6"/>
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
-    </row>
-    <row r="239" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A239" s="45" t="s">
-        <v>379</v>
-      </c>
-      <c r="B239" s="45">
-        <v>3299</v>
-      </c>
-      <c r="C239" s="57" t="s">
-        <v>380</v>
-      </c>
-      <c r="D239" s="43" t="s">
-        <v>381</v>
-      </c>
-      <c r="E239" s="40">
-        <v>5145</v>
-      </c>
-      <c r="F239" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="G239" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H239" s="6"/>
-      <c r="I239" s="5"/>
-      <c r="J239" s="5"/>
     </row>
     <row r="240" spans="1:10" ht="15.75" customHeight="1">
       <c r="A240" s="45" t="s">
@@ -20772,7 +20783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/datos/convenios_semaforo_agosto2026_verificado.xlsx
+++ b/datos/convenios_semaforo_agosto2026_verificado.xlsx
@@ -6278,7 +6278,7 @@
         <v>300</v>
       </c>
       <c r="E173" s="53">
-        <v>34335</v>
+        <v>16830</v>
       </c>
       <c r="F173" s="10"/>
       <c r="G173" s="42"/>
